--- a/docs/analyze/Stage_A_Test_Account_Check_2026-10-07.xlsx
+++ b/docs/analyze/Stage_A_Test_Account_Check_2026-10-07.xlsx
@@ -126,12 +126,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="168">
   <si>
     <t xml:space="preserve">Stage A worksheet: Exact test-account check</t>
   </si>
   <si>
-    <t xml:space="preserve">Prepared 7 October 2026 for the Stage A veto gates (methodology §5.3). Fill in during the check of the Exact test account.</t>
+    <t xml:space="preserve">Prepared 7 October 2026 for the Stage A veto gates (methodology §5.3). Fill in during the check of the Exact test account. Updated 7 October: G1 and G2 answered.</t>
   </si>
   <si>
     <t xml:space="preserve">Purpose</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">How to fill it in</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Start with G1–G3 on the 'Checks' sheet: they need Johan's answer and decide what you may do with the data.</t>
+    <t xml:space="preserve">1. G1 and G2 on the 'Checks' sheet are answered: Johan's permission covers the test-account data and an external AI service (7 October). G3, what to anonymise in the thesis, is still to ask Johan; it sets how results are reported, not whether the data may be used.</t>
   </si>
   <si>
     <t xml:space="preserve">2. Then G4–G8 for the account as a whole, then the rows per candidate.</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">Background</t>
   </si>
   <si>
-    <t xml:space="preserve">Johan permits using data in the Exact test account (reported by Yijie on 2 October). The account holds past cases from an earlier period and is not up to date, which matters for gate 2.</t>
+    <t xml:space="preserve">Johan permits using data in the Exact test account (reported by Yijie on 2 October) and processing its documents with an external AI service (confirmed by Yijie on 7 October). The account holds past cases from an earlier period and is not up to date, which matters for gate 2.</t>
   </si>
   <si>
     <t xml:space="preserve">Progress</t>
@@ -248,27 +248,36 @@
     <t xml:space="preserve">Ask Johan by email and keep the reply.</t>
   </si>
   <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Permission confirmed by Yijie on 7 October. Keep Johan's reply with the project records.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whether test-account documents may be processed by an external AI service (cloud), or only by tools that run locally.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ask Johan, and IT if needed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">External AI service permitted (confirmed by Yijie on 7 October). Note any conditions Johan set, such as which service.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What must be anonymised in the thesis: supplier names, prices, people.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ask Johan.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Not checked</t>
   </si>
   <si>
-    <t xml:space="preserve">G2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whether test-account documents may be processed by an external AI service (cloud), or only by tools that run locally.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ask Johan, and IT if needed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What must be anonymised in the thesis: supplier names, prices, people.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ask Johan.</t>
-  </si>
-  <si>
     <t xml:space="preserve">G4</t>
   </si>
   <si>
@@ -587,13 +596,25 @@
     <t xml:space="preserve">Stage A result</t>
   </si>
   <si>
+    <t xml:space="preserve">Pass</t>
+  </si>
+  <si>
     <t xml:space="preserve">Open</t>
   </si>
   <si>
+    <t xml:space="preserve">Gate 1: G1, G2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gate 1: G1, G2 yes; MX4 (Orbis) open.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gate 1: G1, G2 yes; RI2 (drawing archive) open.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Where the evidence for each gate comes from</t>
   </si>
   <si>
-    <t xml:space="preserve">Checks G1–G3 (Johan).</t>
+    <t xml:space="preserve">Checks G1–G2 (Johan), plus MX4 for maximalisatie and RI2 for request intake. G3 sets how results are anonymised, not whether the data may be used.</t>
   </si>
   <si>
     <t xml:space="preserve">Checks G4, G5, G7 and each candidate's 'Gate 2' rows.</t>
@@ -1113,7 +1134,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -1178,7 +1199,7 @@
       </c>
       <c r="B21" s="4" t="n">
         <f aca="false">COUNTIFS(Checks!F2:F32,"&lt;&gt;Not checked",Checks!F2:F32,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1319,12 +1340,16 @@
       </c>
       <c r="G2" s="10"/>
       <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="11"/>
-    </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I2" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" s="11" t="n">
+        <v>46302</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>36</v>
@@ -1333,22 +1358,26 @@
         <v>37</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>40</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="11"/>
+      <c r="I3" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" s="11" t="n">
+        <v>46302</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>36</v>
@@ -1357,13 +1386,13 @@
         <v>37</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
@@ -1372,22 +1401,22 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
@@ -1396,22 +1425,22 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="10"/>
@@ -1420,22 +1449,22 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
@@ -1444,22 +1473,22 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
@@ -1468,22 +1497,22 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>36</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
@@ -1492,22 +1521,22 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
@@ -1519,19 +1548,19 @@
         <v>24</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
@@ -1540,22 +1569,22 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
@@ -1564,22 +1593,22 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
@@ -1588,22 +1617,22 @@
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
@@ -1612,22 +1641,22 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
@@ -1636,22 +1665,22 @@
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>84</v>
-      </c>
       <c r="D16" s="9" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G16" s="10"/>
       <c r="H16" s="10"/>
@@ -1660,22 +1689,22 @@
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G17" s="10"/>
       <c r="H17" s="10"/>
@@ -1684,22 +1713,22 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G18" s="10"/>
       <c r="H18" s="10"/>
@@ -1708,22 +1737,22 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>95</v>
-      </c>
       <c r="C19" s="9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
@@ -1732,22 +1761,22 @@
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
@@ -1756,22 +1785,22 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G21" s="10"/>
       <c r="H21" s="10"/>
@@ -1780,22 +1809,22 @@
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G22" s="10"/>
       <c r="H22" s="10"/>
@@ -1804,22 +1833,22 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B23" s="9" t="s">
-        <v>108</v>
-      </c>
       <c r="C23" s="9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G23" s="10"/>
       <c r="H23" s="10"/>
@@ -1828,22 +1857,22 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
@@ -1852,22 +1881,22 @@
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>116</v>
-      </c>
       <c r="C25" s="9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>
@@ -1876,22 +1905,22 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G26" s="10"/>
       <c r="H26" s="10"/>
@@ -1900,22 +1929,22 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G27" s="10"/>
       <c r="H27" s="10"/>
@@ -1924,22 +1953,22 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G28" s="10"/>
       <c r="H28" s="10"/>
@@ -1948,22 +1977,22 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G29" s="10"/>
       <c r="H29" s="10"/>
@@ -1972,22 +2001,22 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G30" s="10"/>
       <c r="H30" s="10"/>
@@ -1996,22 +2025,22 @@
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B31" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B31" s="9" t="s">
-        <v>137</v>
-      </c>
       <c r="C31" s="9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G31" s="10"/>
       <c r="H31" s="10"/>
@@ -2020,22 +2049,22 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G32" s="10"/>
       <c r="H32" s="10"/>
@@ -2077,12 +2106,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -2102,56 +2131,58 @@
         <v>37</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="H5" s="10"/>
+        <v>157</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>158</v>
+      </c>
       <c r="I5" s="16" t="n">
         <f aca="false">COUNTIF(B5:G5,"Open")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J5" s="17" t="str">
         <f aca="false">IF(COUNTIF(B5:G5,"Reject")&gt;0,"Reject",IF(COUNTIF(B5:G5,"Open")&gt;0,"Open",IF(COUNTIF(B5:G5,"Redesign")&gt;0,"Redesign","Pass")))</f>
@@ -2160,27 +2191,29 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="H6" s="10"/>
+        <v>157</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>159</v>
+      </c>
       <c r="I6" s="16" t="n">
         <f aca="false">COUNTIF(B6:G6,"Open")</f>
         <v>6</v>
@@ -2192,30 +2225,32 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="H7" s="10"/>
+        <v>157</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>158</v>
+      </c>
       <c r="I7" s="16" t="n">
         <f aca="false">COUNTIF(B7:G7,"Open")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J7" s="17" t="str">
         <f aca="false">IF(COUNTIF(B7:G7,"Reject")&gt;0,"Reject",IF(COUNTIF(B7:G7,"Open")&gt;0,"Open",IF(COUNTIF(B7:G7,"Redesign")&gt;0,"Redesign","Pass")))</f>
@@ -2224,27 +2259,29 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="H8" s="10"/>
+        <v>157</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>160</v>
+      </c>
       <c r="I8" s="16" t="n">
         <f aca="false">COUNTIF(B8:G8,"Open")</f>
         <v>6</v>
@@ -2256,30 +2293,32 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="H9" s="10"/>
+        <v>157</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>158</v>
+      </c>
       <c r="I9" s="16" t="n">
         <f aca="false">COUNTIF(B9:G9,"Open")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J9" s="17" t="str">
         <f aca="false">IF(COUNTIF(B9:G9,"Reject")&gt;0,"Reject",IF(COUNTIF(B9:G9,"Open")&gt;0,"Open",IF(COUNTIF(B9:G9,"Redesign")&gt;0,"Redesign","Pass")))</f>
@@ -2288,30 +2327,32 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="H10" s="10"/>
+        <v>157</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>158</v>
+      </c>
       <c r="I10" s="16" t="n">
         <f aca="false">COUNTIF(B10:G10,"Open")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J10" s="17" t="str">
         <f aca="false">IF(COUNTIF(B10:G10,"Reject")&gt;0,"Reject",IF(COUNTIF(B10:G10,"Open")&gt;0,"Open",IF(COUNTIF(B10:G10,"Redesign")&gt;0,"Redesign","Pass")))</f>
@@ -2320,7 +2361,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2328,7 +2369,7 @@
         <v>37</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
@@ -2341,10 +2382,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
@@ -2357,10 +2398,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
@@ -2373,10 +2414,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
@@ -2389,10 +2430,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C17" s="18"/>
       <c r="D17" s="18"/>
@@ -2405,10 +2446,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C18" s="18"/>
       <c r="D18" s="18"/>

--- a/docs/analyze/Stage_A_Test_Account_Check_2026-10-07.xlsx
+++ b/docs/analyze/Stage_A_Test_Account_Check_2026-10-07.xlsx
@@ -1285,7 +1285,7 @@
       </c>
       <c r="I11" s="30" t="inlineStr">
         <is>
-          <t>One viewer. Completed POs: screenshots of the Bijlage window and status bar, kept outside GitHub (5 of 9 on file); open POs: Yijie's own notes, no screenshots. Wilson 95% interval for 10 of 21: 28% to 68%. One of the 10 confirmations is a file named like the PO (possibly a countersigned PO), still to open. Completed POs are reached through the Bijlage window of the list; the route first used found only open POs. The Bevestigd status agrees with a stored confirmation on 7 of the 9 completed POs (one registered without a stored confirmation, one stored without registration), so it is only a rough proxy. October 2025 is the last month in the copy: repeat on an earlier, complete month.</t>
+          <t>One viewer. Completed POs: screenshots of the Bijlage window and status bar, kept outside GitHub (5 of 9 on file); open POs: Yijie's own notes, no screenshots. Wilson 95% interval for 10 of 21: 28% to 68%. One of the 10 confirmations is stored under the PO's file name; opened by Yijie: it is a supplier confirmation. Completed POs are reached through the Bijlage window of the list; the route first used found only open POs. The Bevestigd status agrees with a stored confirmation on 7 of the 9 completed POs (one registered without a stored confirmation, one stored without registration), so it is only a rough proxy. October 2025 is the last month in the copy: repeat on an earlier, complete month.</t>
         </is>
       </c>
       <c r="J11" s="31" t="n">
